--- a/resources/contact_mtx_hun.xlsx
+++ b/resources/contact_mtx_hun.xlsx
@@ -8,16 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CSURITA\PycharmProjects\PythonProject\counterfactual-analysis-vzv\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E80E019-023B-44A5-9F0F-2A9CF192D022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D76A37-1F47-4B49-9DEF-5A0EEAE41415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="320" yWindow="1620" windowWidth="18880" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="400" yWindow="890" windowWidth="18880" windowHeight="9660" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="contacts" sheetId="2" r:id="rId1"/>
-    <sheet name="contacts_original" sheetId="1" r:id="rId2"/>
+    <sheet name="contacts11" sheetId="3" r:id="rId2"/>
+    <sheet name="contacts16" sheetId="4" r:id="rId3"/>
+    <sheet name="contacts_original" sheetId="1" r:id="rId4"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
   <si>
     <t>10-14</t>
   </si>
@@ -69,6 +71,12 @@
   </si>
   <si>
     <t>20+</t>
+  </si>
+  <si>
+    <t>10+</t>
+  </si>
+  <si>
+    <t>15+</t>
   </si>
 </sst>
 </file>
@@ -135,7 +143,7 @@
       <sheetName val="Munka1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
+      <sheetData sheetId="0" refreshError="1">
         <row r="1">
           <cell r="A1">
             <v>2.8526575723699183</v>
@@ -1306,7 +1314,7 @@
         <v>6.2645778017866763E-2</v>
       </c>
       <c r="N2" cm="1">
-        <f t="array" ref="N2">SUM(INDEX(contacts_original!$A$1:$O$15,
+        <f t="array" ref="N2">SUM(INDEX(contacts_original!$A$1:$P$16,
            INT((ROW(N2)-2)/5)+1,
            INT((COLUMN(N2)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
         <v>4.8222265119435823</v>
@@ -1365,7 +1373,7 @@
         <v>6.2645778017866763E-2</v>
       </c>
       <c r="N3" cm="1">
-        <f t="array" ref="N3">SUM(INDEX(contacts_original!$A$1:$O$15,
+        <f t="array" ref="N3">SUM(INDEX(contacts_original!$A$1:$P$16,
            INT((ROW(N3)-2)/5)+1,
            INT((COLUMN(N3)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
         <v>4.8222265119435823</v>
@@ -1424,7 +1432,7 @@
         <v>6.2645778017866763E-2</v>
       </c>
       <c r="N4" cm="1">
-        <f t="array" ref="N4">SUM(INDEX(contacts_original!$A$1:$O$15,
+        <f t="array" ref="N4">SUM(INDEX(contacts_original!$A$1:$P$16,
            INT((ROW(N4)-2)/5)+1,
            INT((COLUMN(N4)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
         <v>4.8222265119435823</v>
@@ -1483,7 +1491,7 @@
         <v>6.2645778017866763E-2</v>
       </c>
       <c r="N5" cm="1">
-        <f t="array" ref="N5">SUM(INDEX(contacts_original!$A$1:$O$15,
+        <f t="array" ref="N5">SUM(INDEX(contacts_original!$A$1:$P$16,
            INT((ROW(N5)-2)/5)+1,
            INT((COLUMN(N5)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
         <v>4.8222265119435823</v>
@@ -1542,7 +1550,7 @@
         <v>6.2645778017866763E-2</v>
       </c>
       <c r="N6" cm="1">
-        <f t="array" ref="N6">SUM(INDEX(contacts_original!$A$1:$O$15,
+        <f t="array" ref="N6">SUM(INDEX(contacts_original!$A$1:$P$16,
            INT((ROW(N6)-2)/5)+1,
            INT((COLUMN(N6)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
         <v>4.8222265119435823</v>
@@ -1601,7 +1609,7 @@
         <v>0.15644692283686498</v>
       </c>
       <c r="N7" cm="1">
-        <f t="array" ref="N7">SUM(INDEX(contacts_original!$A$1:$O$15,
+        <f t="array" ref="N7">SUM(INDEX(contacts_original!$A$1:$P$16,
            INT((ROW(N7)-2)/5)+1,
            INT((COLUMN(N7)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
         <v>4.9326734169754829</v>
@@ -1660,7 +1668,7 @@
         <v>0.15644692283686498</v>
       </c>
       <c r="N8" cm="1">
-        <f t="array" ref="N8">SUM(INDEX(contacts_original!$A$1:$O$15,
+        <f t="array" ref="N8">SUM(INDEX(contacts_original!$A$1:$P$16,
            INT((ROW(N8)-2)/5)+1,
            INT((COLUMN(N8)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
         <v>4.9326734169754829</v>
@@ -1719,7 +1727,7 @@
         <v>0.15644692283686498</v>
       </c>
       <c r="N9" cm="1">
-        <f t="array" ref="N9">SUM(INDEX(contacts_original!$A$1:$O$15,
+        <f t="array" ref="N9">SUM(INDEX(contacts_original!$A$1:$P$16,
            INT((ROW(N9)-2)/5)+1,
            INT((COLUMN(N9)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
         <v>4.9326734169754829</v>
@@ -1778,7 +1786,7 @@
         <v>0.15644692283686498</v>
       </c>
       <c r="N10" cm="1">
-        <f t="array" ref="N10">SUM(INDEX(contacts_original!$A$1:$O$15,
+        <f t="array" ref="N10">SUM(INDEX(contacts_original!$A$1:$P$16,
            INT((ROW(N10)-2)/5)+1,
            INT((COLUMN(N10)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
         <v>4.9326734169754829</v>
@@ -1837,7 +1845,7 @@
         <v>0.15644692283686498</v>
       </c>
       <c r="N11" cm="1">
-        <f t="array" ref="N11">SUM(INDEX(contacts_original!$A$1:$O$15,
+        <f t="array" ref="N11">SUM(INDEX(contacts_original!$A$1:$P$16,
            INT((ROW(N11)-2)/5)+1,
            INT((COLUMN(N11)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
         <v>4.9326734169754829</v>
@@ -1896,7 +1904,7 @@
         <v>1.1920094334633184</v>
       </c>
       <c r="N12" cm="1">
-        <f t="array" ref="N12">SUM(INDEX(contacts_original!$A$1:$O$15,
+        <f t="array" ref="N12">SUM(INDEX(contacts_original!$A$1:$P$16,
            INT((ROW(N12)-2)/5)+1,
            INT((COLUMN(N12)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
         <v>10.234438581488178</v>
@@ -1955,7 +1963,7 @@
         <v>1.1920094334633184</v>
       </c>
       <c r="N13" cm="1">
-        <f t="array" ref="N13">SUM(INDEX(contacts_original!$A$1:$O$15,
+        <f t="array" ref="N13">SUM(INDEX(contacts_original!$A$1:$P$16,
            INT((ROW(N13)-2)/5)+1,
            INT((COLUMN(N13)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
         <v>10.234438581488178</v>
@@ -1966,73 +1974,73 @@
         <v>2</v>
       </c>
       <c r="B14" cm="1">
-        <f t="array" ref="B14">SUM(INDEX(contacts_original!$A$1:$O$15,
+        <f t="array" ref="B14">SUM(INDEX(contacts_original!$A$1:$P$16,
 INT((ROW(B14)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
 INT((COLUMN(B14)/5)+1)))</f>
         <v>4.9184518804057058</v>
       </c>
       <c r="C14" cm="1">
-        <f t="array" ref="C14">SUM(INDEX(contacts_original!$A$1:$O$15,
+        <f t="array" ref="C14">SUM(INDEX(contacts_original!$A$1:$P$16,
 INT((ROW(C14)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
 INT((COLUMN(C14)/5)+1)))</f>
         <v>4.9184518804057058</v>
       </c>
       <c r="D14" cm="1">
-        <f t="array" ref="D14">SUM(INDEX(contacts_original!$A$1:$O$15,
+        <f t="array" ref="D14">SUM(INDEX(contacts_original!$A$1:$P$16,
 INT((ROW(D14)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
 INT((COLUMN(D14)/5)+1)))</f>
         <v>4.9184518804057058</v>
       </c>
       <c r="E14" cm="1">
-        <f t="array" ref="E14">SUM(INDEX(contacts_original!$A$1:$O$15,
+        <f t="array" ref="E14">SUM(INDEX(contacts_original!$A$1:$P$16,
 INT((ROW(E14)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
 INT((COLUMN(E14)/5)+1)))</f>
         <v>7.9834252529999645</v>
       </c>
       <c r="F14" cm="1">
-        <f t="array" ref="F14">SUM(INDEX(contacts_original!$A$1:$O$15,
+        <f t="array" ref="F14">SUM(INDEX(contacts_original!$A$1:$P$16,
 INT((ROW(F14)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
 INT((COLUMN(F14)/5)+1)))</f>
         <v>7.9834252529999645</v>
       </c>
       <c r="G14" cm="1">
-        <f t="array" ref="G14">SUM(INDEX(contacts_original!$A$1:$O$15,
+        <f t="array" ref="G14">SUM(INDEX(contacts_original!$A$1:$P$16,
 INT((ROW(G14)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
 INT((COLUMN(G14)/5)+1)))</f>
         <v>7.9834252529999645</v>
       </c>
       <c r="H14" cm="1">
-        <f t="array" ref="H14">SUM(INDEX(contacts_original!$A$1:$O$15,
+        <f t="array" ref="H14">SUM(INDEX(contacts_original!$A$1:$P$16,
 INT((ROW(H14)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
 INT((COLUMN(H14)/5)+1)))</f>
         <v>7.9834252529999645</v>
       </c>
       <c r="I14" cm="1">
-        <f t="array" ref="I14">SUM(INDEX(contacts_original!$A$1:$O$15,
+        <f t="array" ref="I14">SUM(INDEX(contacts_original!$A$1:$P$16,
 INT((ROW(I14)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
 INT((COLUMN(I14)/5)+1)))</f>
         <v>7.9834252529999645</v>
       </c>
       <c r="J14" cm="1">
-        <f t="array" ref="J14">SUM(INDEX(contacts_original!$A$1:$O$15,
+        <f t="array" ref="J14">SUM(INDEX(contacts_original!$A$1:$P$16,
 INT((ROW(J14)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
 INT((COLUMN(J14)/5)+1)))</f>
         <v>14.188927371612026</v>
       </c>
       <c r="K14" cm="1">
-        <f t="array" ref="K14">SUM(INDEX(contacts_original!$A$1:$O$15,
+        <f t="array" ref="K14">SUM(INDEX(contacts_original!$A$1:$P$16,
 INT((ROW(K14)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
 INT((COLUMN(K14)/5)+1)))</f>
         <v>14.188927371612026</v>
       </c>
       <c r="L14" cm="1">
-        <f t="array" ref="L14">SUM(INDEX(contacts_original!$A$1:$O$15,
+        <f t="array" ref="L14">SUM(INDEX(contacts_original!$A$1:$P$16,
 INT((ROW(L14)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
 INT((COLUMN(L14)/5)+1)))</f>
         <v>14.188927371612026</v>
       </c>
       <c r="M14" cm="1">
-        <f t="array" ref="M14">SUM(INDEX(contacts_original!$A$1:$O$15,
+        <f t="array" ref="M14">SUM(INDEX(contacts_original!$A$1:$P$16,
 INT((ROW(M14)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
 INT((COLUMN(M14)/5)+1)))</f>
         <v>14.188927371612026</v>
@@ -2048,6 +2056,1856 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4267623E-AFD5-49E1-818C-45481FF8ACA4}">
+  <dimension ref="A1:L12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(B2)-2)/5)+1,INT((COLUMN(B2)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="C2">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(C2)-2)/5)+1,INT((COLUMN(C2)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="D2">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(D2)-2)/5)+1,INT((COLUMN(D2)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="E2">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(E2)-2)/5)+1,INT((COLUMN(E2)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="F2">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(F2)-2)/5)+1,INT((COLUMN(F2)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="G2">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(G2)-2)/5)+1,INT((COLUMN(G2)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="H2">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(H2)-2)/5)+1,INT((COLUMN(H2)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="I2">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(I2)-2)/5)+1,INT((COLUMN(I2)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="J2">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(J2)-2)/5)+1,INT((COLUMN(J2)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="K2">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(K2)-2)/5)+1,INT((COLUMN(K2)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="L2" cm="1">
+        <f t="array" ref="L2">SUM(INDEX(contacts_original!$A$1:$P$16,
+           INT((ROW(L2)-2)/5)+1,
+           INT((COLUMN(L2)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
+        <v>4.8222265119435823</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(B3)-2)/5)+1,INT((COLUMN(B3)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="C3">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(C3)-2)/5)+1,INT((COLUMN(C3)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="D3">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(D3)-2)/5)+1,INT((COLUMN(D3)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="E3">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(E3)-2)/5)+1,INT((COLUMN(E3)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="F3">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(F3)-2)/5)+1,INT((COLUMN(F3)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="G3">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(G3)-2)/5)+1,INT((COLUMN(G3)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="H3">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(H3)-2)/5)+1,INT((COLUMN(H3)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="I3">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(I3)-2)/5)+1,INT((COLUMN(I3)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="J3">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(J3)-2)/5)+1,INT((COLUMN(J3)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="K3">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(K3)-2)/5)+1,INT((COLUMN(K3)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="L3" cm="1">
+        <f t="array" ref="L3">SUM(INDEX(contacts_original!$A$1:$P$16,
+           INT((ROW(L3)-2)/5)+1,
+           INT((COLUMN(L3)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
+        <v>4.8222265119435823</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(B4)-2)/5)+1,INT((COLUMN(B4)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="C4">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(C4)-2)/5)+1,INT((COLUMN(C4)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="D4">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(D4)-2)/5)+1,INT((COLUMN(D4)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="E4">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(E4)-2)/5)+1,INT((COLUMN(E4)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="F4">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(F4)-2)/5)+1,INT((COLUMN(F4)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="G4">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(G4)-2)/5)+1,INT((COLUMN(G4)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="H4">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(H4)-2)/5)+1,INT((COLUMN(H4)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="I4">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(I4)-2)/5)+1,INT((COLUMN(I4)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="J4">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(J4)-2)/5)+1,INT((COLUMN(J4)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="K4">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(K4)-2)/5)+1,INT((COLUMN(K4)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="L4" cm="1">
+        <f t="array" ref="L4">SUM(INDEX(contacts_original!$A$1:$P$16,
+           INT((ROW(L4)-2)/5)+1,
+           INT((COLUMN(L4)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
+        <v>4.8222265119435823</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(B5)-2)/5)+1,INT((COLUMN(B5)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="C5">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(C5)-2)/5)+1,INT((COLUMN(C5)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="D5">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(D5)-2)/5)+1,INT((COLUMN(D5)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="E5">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(E5)-2)/5)+1,INT((COLUMN(E5)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="F5">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(F5)-2)/5)+1,INT((COLUMN(F5)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="G5">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(G5)-2)/5)+1,INT((COLUMN(G5)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="H5">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(H5)-2)/5)+1,INT((COLUMN(H5)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="I5">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(I5)-2)/5)+1,INT((COLUMN(I5)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="J5">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(J5)-2)/5)+1,INT((COLUMN(J5)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="K5">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(K5)-2)/5)+1,INT((COLUMN(K5)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="L5" cm="1">
+        <f t="array" ref="L5">SUM(INDEX(contacts_original!$A$1:$P$16,
+           INT((ROW(L5)-2)/5)+1,
+           INT((COLUMN(L5)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
+        <v>4.8222265119435823</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(B6)-2)/5)+1,INT((COLUMN(B6)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="C6">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(C6)-2)/5)+1,INT((COLUMN(C6)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="D6">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(D6)-2)/5)+1,INT((COLUMN(D6)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="E6">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(E6)-2)/5)+1,INT((COLUMN(E6)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="F6">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(F6)-2)/5)+1,INT((COLUMN(F6)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="G6">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(G6)-2)/5)+1,INT((COLUMN(G6)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="H6">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(H6)-2)/5)+1,INT((COLUMN(H6)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="I6">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(I6)-2)/5)+1,INT((COLUMN(I6)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="J6">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(J6)-2)/5)+1,INT((COLUMN(J6)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="K6">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(K6)-2)/5)+1,INT((COLUMN(K6)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="L6" cm="1">
+        <f t="array" ref="L6">SUM(INDEX(contacts_original!$A$1:$P$16,
+           INT((ROW(L6)-2)/5)+1,
+           INT((COLUMN(L6)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
+        <v>4.8222265119435823</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(B7)-2)/5)+1,INT((COLUMN(B7)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="C7">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(C7)-2)/5)+1,INT((COLUMN(C7)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="D7">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(D7)-2)/5)+1,INT((COLUMN(D7)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="E7">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(E7)-2)/5)+1,INT((COLUMN(E7)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="F7">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(F7)-2)/5)+1,INT((COLUMN(F7)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="G7">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(G7)-2)/5)+1,INT((COLUMN(G7)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="H7">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(H7)-2)/5)+1,INT((COLUMN(H7)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="I7">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(I7)-2)/5)+1,INT((COLUMN(I7)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="J7">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(J7)-2)/5)+1,INT((COLUMN(J7)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="K7">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(K7)-2)/5)+1,INT((COLUMN(K7)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="L7" cm="1">
+        <f t="array" ref="L7">SUM(INDEX(contacts_original!$A$1:$P$16,
+           INT((ROW(L7)-2)/5)+1,
+           INT((COLUMN(L7)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
+        <v>4.9326734169754829</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(B8)-2)/5)+1,INT((COLUMN(B8)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="C8">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(C8)-2)/5)+1,INT((COLUMN(C8)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="D8">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(D8)-2)/5)+1,INT((COLUMN(D8)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="E8">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(E8)-2)/5)+1,INT((COLUMN(E8)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="F8">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(F8)-2)/5)+1,INT((COLUMN(F8)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="G8">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(G8)-2)/5)+1,INT((COLUMN(G8)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="H8">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(H8)-2)/5)+1,INT((COLUMN(H8)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="I8">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(I8)-2)/5)+1,INT((COLUMN(I8)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="J8">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(J8)-2)/5)+1,INT((COLUMN(J8)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="K8">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(K8)-2)/5)+1,INT((COLUMN(K8)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="L8" cm="1">
+        <f t="array" ref="L8">SUM(INDEX(contacts_original!$A$1:$P$16,
+           INT((ROW(L8)-2)/5)+1,
+           INT((COLUMN(L8)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
+        <v>4.9326734169754829</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(B9)-2)/5)+1,INT((COLUMN(B9)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="C9">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(C9)-2)/5)+1,INT((COLUMN(C9)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="D9">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(D9)-2)/5)+1,INT((COLUMN(D9)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="E9">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(E9)-2)/5)+1,INT((COLUMN(E9)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="F9">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(F9)-2)/5)+1,INT((COLUMN(F9)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="G9">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(G9)-2)/5)+1,INT((COLUMN(G9)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="H9">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(H9)-2)/5)+1,INT((COLUMN(H9)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="I9">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(I9)-2)/5)+1,INT((COLUMN(I9)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="J9">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(J9)-2)/5)+1,INT((COLUMN(J9)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="K9">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(K9)-2)/5)+1,INT((COLUMN(K9)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="L9" cm="1">
+        <f t="array" ref="L9">SUM(INDEX(contacts_original!$A$1:$P$16,
+           INT((ROW(L9)-2)/5)+1,
+           INT((COLUMN(L9)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
+        <v>4.9326734169754829</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(B10)-2)/5)+1,INT((COLUMN(B10)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="C10">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(C10)-2)/5)+1,INT((COLUMN(C10)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="D10">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(D10)-2)/5)+1,INT((COLUMN(D10)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="E10">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(E10)-2)/5)+1,INT((COLUMN(E10)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="F10">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(F10)-2)/5)+1,INT((COLUMN(F10)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="G10">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(G10)-2)/5)+1,INT((COLUMN(G10)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="H10">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(H10)-2)/5)+1,INT((COLUMN(H10)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="I10">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(I10)-2)/5)+1,INT((COLUMN(I10)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="J10">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(J10)-2)/5)+1,INT((COLUMN(J10)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="K10">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(K10)-2)/5)+1,INT((COLUMN(K10)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="L10" cm="1">
+        <f t="array" ref="L10">SUM(INDEX(contacts_original!$A$1:$P$16,
+           INT((ROW(L10)-2)/5)+1,
+           INT((COLUMN(L10)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
+        <v>4.9326734169754829</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(B11)-2)/5)+1,INT((COLUMN(B11)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="C11">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(C11)-2)/5)+1,INT((COLUMN(C11)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="D11">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(D11)-2)/5)+1,INT((COLUMN(D11)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="E11">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(E11)-2)/5)+1,INT((COLUMN(E11)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="F11">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(F11)-2)/5)+1,INT((COLUMN(F11)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="G11">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(G11)-2)/5)+1,INT((COLUMN(G11)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="H11">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(H11)-2)/5)+1,INT((COLUMN(H11)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="I11">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(I11)-2)/5)+1,INT((COLUMN(I11)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="J11">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(J11)-2)/5)+1,INT((COLUMN(J11)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="K11">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(K11)-2)/5)+1,INT((COLUMN(K11)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="L11" cm="1">
+        <f t="array" ref="L11">SUM(INDEX(contacts_original!$A$1:$P$16,
+           INT((ROW(L11)-2)/5)+1,
+           INT((COLUMN(L11)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
+        <v>4.9326734169754829</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" cm="1">
+        <f t="array" ref="B12">SUM(INDEX(contacts_original!$A$1:$P$16,
+INT((ROW(B12)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
+INT((COLUMN(B12)/5)+1)))</f>
+        <v>4.9184518804057058</v>
+      </c>
+      <c r="C12" cm="1">
+        <f t="array" ref="C12">SUM(INDEX(contacts_original!$A$1:$P$16,
+INT((ROW(C12)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
+INT((COLUMN(C12)/5)+1)))</f>
+        <v>4.9184518804057058</v>
+      </c>
+      <c r="D12" cm="1">
+        <f t="array" ref="D12">SUM(INDEX(contacts_original!$A$1:$P$16,
+INT((ROW(D12)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
+INT((COLUMN(D12)/5)+1)))</f>
+        <v>4.9184518804057058</v>
+      </c>
+      <c r="E12" cm="1">
+        <f t="array" ref="E12">SUM(INDEX(contacts_original!$A$1:$P$16,
+INT((ROW(E12)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
+INT((COLUMN(E12)/5)+1)))</f>
+        <v>7.9834252529999645</v>
+      </c>
+      <c r="F12" cm="1">
+        <f t="array" ref="F12">SUM(INDEX(contacts_original!$A$1:$P$16,
+INT((ROW(F12)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
+INT((COLUMN(F12)/5)+1)))</f>
+        <v>7.9834252529999645</v>
+      </c>
+      <c r="G12" cm="1">
+        <f t="array" ref="G12">SUM(INDEX(contacts_original!$A$1:$P$16,
+INT((ROW(G12)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
+INT((COLUMN(G12)/5)+1)))</f>
+        <v>7.9834252529999645</v>
+      </c>
+      <c r="H12" cm="1">
+        <f t="array" ref="H12">SUM(INDEX(contacts_original!$A$1:$P$16,
+INT((ROW(H12)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
+INT((COLUMN(H12)/5)+1)))</f>
+        <v>7.9834252529999645</v>
+      </c>
+      <c r="I12" cm="1">
+        <f t="array" ref="I12">SUM(INDEX(contacts_original!$A$1:$P$16,
+INT((ROW(I12)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
+INT((COLUMN(I12)/5)+1)))</f>
+        <v>7.9834252529999645</v>
+      </c>
+      <c r="J12" cm="1">
+        <f t="array" ref="J12">SUM(INDEX(contacts_original!$A$1:$P$16,
+INT((ROW(J12)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
+INT((COLUMN(J12)/5)+1)))</f>
+        <v>14.188927371612026</v>
+      </c>
+      <c r="K12" cm="1">
+        <f t="array" ref="K12">SUM(INDEX(contacts_original!$A$1:$P$16,
+INT((ROW(K12)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
+INT((COLUMN(K12)/5)+1)))</f>
+        <v>14.188927371612026</v>
+      </c>
+      <c r="L12">
+        <f>SUM(contacts_original!C3:P16)/(ROW(P16)-ROW(C3))</f>
+        <v>12.339129006391877</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B55EA2DB-D7F5-4799-A9EB-09CAE596CC31}">
+  <dimension ref="A1:Q17"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(B2)-2)/5)+1,INT((COLUMN(B2)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="C2">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(C2)-2)/5)+1,INT((COLUMN(C2)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="D2">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(D2)-2)/5)+1,INT((COLUMN(D2)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="E2">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(E2)-2)/5)+1,INT((COLUMN(E2)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="F2">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(F2)-2)/5)+1,INT((COLUMN(F2)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="G2">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(G2)-2)/5)+1,INT((COLUMN(G2)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="H2">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(H2)-2)/5)+1,INT((COLUMN(H2)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="I2">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(I2)-2)/5)+1,INT((COLUMN(I2)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="J2">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(J2)-2)/5)+1,INT((COLUMN(J2)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="K2">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(K2)-2)/5)+1,INT((COLUMN(K2)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="L2">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(L2)-2)/5)+1,INT((COLUMN(L2)-2)/5)+1)/5</f>
+        <v>6.2645778017866763E-2</v>
+      </c>
+      <c r="M2">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(M2)-2)/5)+1,INT((COLUMN(M2)-2)/5)+1)/5</f>
+        <v>6.2645778017866763E-2</v>
+      </c>
+      <c r="N2">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(N2)-2)/5)+1,INT((COLUMN(N2)-2)/5)+1)/5</f>
+        <v>6.2645778017866763E-2</v>
+      </c>
+      <c r="O2">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(O2)-2)/5)+1,INT((COLUMN(O2)-2)/5)+1)/5</f>
+        <v>6.2645778017866763E-2</v>
+      </c>
+      <c r="P2">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(P2)-2)/5)+1,INT((COLUMN(P2)-2)/5)+1)/5</f>
+        <v>6.2645778017866763E-2</v>
+      </c>
+      <c r="Q2" cm="1">
+        <f t="array" ref="Q2">SUM(INDEX(contacts_original!$A$1:$P$16,
+           INT((ROW(Q2)-2)/5)+1,
+           INT((COLUMN(Q2)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
+        <v>4.5549761565634022</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(B3)-2)/5)+1,INT((COLUMN(B3)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="C3">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(C3)-2)/5)+1,INT((COLUMN(C3)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="D3">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(D3)-2)/5)+1,INT((COLUMN(D3)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="E3">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(E3)-2)/5)+1,INT((COLUMN(E3)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="F3">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(F3)-2)/5)+1,INT((COLUMN(F3)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="G3">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(G3)-2)/5)+1,INT((COLUMN(G3)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="H3">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(H3)-2)/5)+1,INT((COLUMN(H3)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="I3">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(I3)-2)/5)+1,INT((COLUMN(I3)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="J3">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(J3)-2)/5)+1,INT((COLUMN(J3)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="K3">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(K3)-2)/5)+1,INT((COLUMN(K3)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="L3">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(L3)-2)/5)+1,INT((COLUMN(L3)-2)/5)+1)/5</f>
+        <v>6.2645778017866763E-2</v>
+      </c>
+      <c r="M3">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(M3)-2)/5)+1,INT((COLUMN(M3)-2)/5)+1)/5</f>
+        <v>6.2645778017866763E-2</v>
+      </c>
+      <c r="N3">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(N3)-2)/5)+1,INT((COLUMN(N3)-2)/5)+1)/5</f>
+        <v>6.2645778017866763E-2</v>
+      </c>
+      <c r="O3">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(O3)-2)/5)+1,INT((COLUMN(O3)-2)/5)+1)/5</f>
+        <v>6.2645778017866763E-2</v>
+      </c>
+      <c r="P3">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(P3)-2)/5)+1,INT((COLUMN(P3)-2)/5)+1)/5</f>
+        <v>6.2645778017866763E-2</v>
+      </c>
+      <c r="Q3" cm="1">
+        <f t="array" ref="Q3">SUM(INDEX(contacts_original!$A$1:$P$16,
+           INT((ROW(Q3)-2)/5)+1,
+           INT((COLUMN(Q3)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
+        <v>4.5549761565634022</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(B4)-2)/5)+1,INT((COLUMN(B4)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="C4">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(C4)-2)/5)+1,INT((COLUMN(C4)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="D4">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(D4)-2)/5)+1,INT((COLUMN(D4)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="E4">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(E4)-2)/5)+1,INT((COLUMN(E4)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="F4">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(F4)-2)/5)+1,INT((COLUMN(F4)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="G4">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(G4)-2)/5)+1,INT((COLUMN(G4)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="H4">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(H4)-2)/5)+1,INT((COLUMN(H4)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="I4">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(I4)-2)/5)+1,INT((COLUMN(I4)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="J4">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(J4)-2)/5)+1,INT((COLUMN(J4)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="K4">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(K4)-2)/5)+1,INT((COLUMN(K4)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="L4">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(L4)-2)/5)+1,INT((COLUMN(L4)-2)/5)+1)/5</f>
+        <v>6.2645778017866763E-2</v>
+      </c>
+      <c r="M4">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(M4)-2)/5)+1,INT((COLUMN(M4)-2)/5)+1)/5</f>
+        <v>6.2645778017866763E-2</v>
+      </c>
+      <c r="N4">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(N4)-2)/5)+1,INT((COLUMN(N4)-2)/5)+1)/5</f>
+        <v>6.2645778017866763E-2</v>
+      </c>
+      <c r="O4">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(O4)-2)/5)+1,INT((COLUMN(O4)-2)/5)+1)/5</f>
+        <v>6.2645778017866763E-2</v>
+      </c>
+      <c r="P4">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(P4)-2)/5)+1,INT((COLUMN(P4)-2)/5)+1)/5</f>
+        <v>6.2645778017866763E-2</v>
+      </c>
+      <c r="Q4" cm="1">
+        <f t="array" ref="Q4">SUM(INDEX(contacts_original!$A$1:$P$16,
+           INT((ROW(Q4)-2)/5)+1,
+           INT((COLUMN(Q4)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
+        <v>4.5549761565634022</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(B5)-2)/5)+1,INT((COLUMN(B5)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="C5">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(C5)-2)/5)+1,INT((COLUMN(C5)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="D5">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(D5)-2)/5)+1,INT((COLUMN(D5)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="E5">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(E5)-2)/5)+1,INT((COLUMN(E5)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="F5">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(F5)-2)/5)+1,INT((COLUMN(F5)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="G5">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(G5)-2)/5)+1,INT((COLUMN(G5)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="H5">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(H5)-2)/5)+1,INT((COLUMN(H5)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="I5">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(I5)-2)/5)+1,INT((COLUMN(I5)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="J5">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(J5)-2)/5)+1,INT((COLUMN(J5)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="K5">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(K5)-2)/5)+1,INT((COLUMN(K5)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="L5">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(L5)-2)/5)+1,INT((COLUMN(L5)-2)/5)+1)/5</f>
+        <v>6.2645778017866763E-2</v>
+      </c>
+      <c r="M5">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(M5)-2)/5)+1,INT((COLUMN(M5)-2)/5)+1)/5</f>
+        <v>6.2645778017866763E-2</v>
+      </c>
+      <c r="N5">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(N5)-2)/5)+1,INT((COLUMN(N5)-2)/5)+1)/5</f>
+        <v>6.2645778017866763E-2</v>
+      </c>
+      <c r="O5">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(O5)-2)/5)+1,INT((COLUMN(O5)-2)/5)+1)/5</f>
+        <v>6.2645778017866763E-2</v>
+      </c>
+      <c r="P5">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(P5)-2)/5)+1,INT((COLUMN(P5)-2)/5)+1)/5</f>
+        <v>6.2645778017866763E-2</v>
+      </c>
+      <c r="Q5" cm="1">
+        <f t="array" ref="Q5">SUM(INDEX(contacts_original!$A$1:$P$16,
+           INT((ROW(Q5)-2)/5)+1,
+           INT((COLUMN(Q5)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
+        <v>4.5549761565634022</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(B6)-2)/5)+1,INT((COLUMN(B6)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="C6">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(C6)-2)/5)+1,INT((COLUMN(C6)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="D6">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(D6)-2)/5)+1,INT((COLUMN(D6)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="E6">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(E6)-2)/5)+1,INT((COLUMN(E6)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="F6">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(F6)-2)/5)+1,INT((COLUMN(F6)-2)/5)+1)/5</f>
+        <v>0.57053151447398365</v>
+      </c>
+      <c r="G6">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(G6)-2)/5)+1,INT((COLUMN(G6)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="H6">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(H6)-2)/5)+1,INT((COLUMN(H6)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="I6">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(I6)-2)/5)+1,INT((COLUMN(I6)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="J6">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(J6)-2)/5)+1,INT((COLUMN(J6)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="K6">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(K6)-2)/5)+1,INT((COLUMN(K6)-2)/5)+1)/5</f>
+        <v>0.15760122474608868</v>
+      </c>
+      <c r="L6">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(L6)-2)/5)+1,INT((COLUMN(L6)-2)/5)+1)/5</f>
+        <v>6.2645778017866763E-2</v>
+      </c>
+      <c r="M6">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(M6)-2)/5)+1,INT((COLUMN(M6)-2)/5)+1)/5</f>
+        <v>6.2645778017866763E-2</v>
+      </c>
+      <c r="N6">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(N6)-2)/5)+1,INT((COLUMN(N6)-2)/5)+1)/5</f>
+        <v>6.2645778017866763E-2</v>
+      </c>
+      <c r="O6">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(O6)-2)/5)+1,INT((COLUMN(O6)-2)/5)+1)/5</f>
+        <v>6.2645778017866763E-2</v>
+      </c>
+      <c r="P6">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(P6)-2)/5)+1,INT((COLUMN(P6)-2)/5)+1)/5</f>
+        <v>6.2645778017866763E-2</v>
+      </c>
+      <c r="Q6" cm="1">
+        <f t="array" ref="Q6">SUM(INDEX(contacts_original!$A$1:$P$16,
+           INT((ROW(Q6)-2)/5)+1,
+           INT((COLUMN(Q6)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
+        <v>4.5549761565634022</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(B7)-2)/5)+1,INT((COLUMN(B7)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="C7">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(C7)-2)/5)+1,INT((COLUMN(C7)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="D7">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(D7)-2)/5)+1,INT((COLUMN(D7)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="E7">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(E7)-2)/5)+1,INT((COLUMN(E7)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="F7">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(F7)-2)/5)+1,INT((COLUMN(F7)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="G7">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(G7)-2)/5)+1,INT((COLUMN(G7)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="H7">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(H7)-2)/5)+1,INT((COLUMN(H7)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="I7">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(I7)-2)/5)+1,INT((COLUMN(I7)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="J7">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(J7)-2)/5)+1,INT((COLUMN(J7)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="K7">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(K7)-2)/5)+1,INT((COLUMN(K7)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="L7">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(L7)-2)/5)+1,INT((COLUMN(L7)-2)/5)+1)/5</f>
+        <v>0.15644692283686498</v>
+      </c>
+      <c r="M7">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(M7)-2)/5)+1,INT((COLUMN(M7)-2)/5)+1)/5</f>
+        <v>0.15644692283686498</v>
+      </c>
+      <c r="N7">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(N7)-2)/5)+1,INT((COLUMN(N7)-2)/5)+1)/5</f>
+        <v>0.15644692283686498</v>
+      </c>
+      <c r="O7">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(O7)-2)/5)+1,INT((COLUMN(O7)-2)/5)+1)/5</f>
+        <v>0.15644692283686498</v>
+      </c>
+      <c r="P7">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(P7)-2)/5)+1,INT((COLUMN(P7)-2)/5)+1)/5</f>
+        <v>0.15644692283686498</v>
+      </c>
+      <c r="Q7" cm="1">
+        <f t="array" ref="Q7">SUM(INDEX(contacts_original!$A$1:$P$16,
+           INT((ROW(Q7)-2)/5)+1,
+           INT((COLUMN(Q7)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
+        <v>4.1986461209260852</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(B8)-2)/5)+1,INT((COLUMN(B8)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="C8">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(C8)-2)/5)+1,INT((COLUMN(C8)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="D8">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(D8)-2)/5)+1,INT((COLUMN(D8)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="E8">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(E8)-2)/5)+1,INT((COLUMN(E8)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="F8">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(F8)-2)/5)+1,INT((COLUMN(F8)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="G8">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(G8)-2)/5)+1,INT((COLUMN(G8)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="H8">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(H8)-2)/5)+1,INT((COLUMN(H8)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="I8">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(I8)-2)/5)+1,INT((COLUMN(I8)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="J8">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(J8)-2)/5)+1,INT((COLUMN(J8)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="K8">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(K8)-2)/5)+1,INT((COLUMN(K8)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="L8">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(L8)-2)/5)+1,INT((COLUMN(L8)-2)/5)+1)/5</f>
+        <v>0.15644692283686498</v>
+      </c>
+      <c r="M8">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(M8)-2)/5)+1,INT((COLUMN(M8)-2)/5)+1)/5</f>
+        <v>0.15644692283686498</v>
+      </c>
+      <c r="N8">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(N8)-2)/5)+1,INT((COLUMN(N8)-2)/5)+1)/5</f>
+        <v>0.15644692283686498</v>
+      </c>
+      <c r="O8">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(O8)-2)/5)+1,INT((COLUMN(O8)-2)/5)+1)/5</f>
+        <v>0.15644692283686498</v>
+      </c>
+      <c r="P8">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(P8)-2)/5)+1,INT((COLUMN(P8)-2)/5)+1)/5</f>
+        <v>0.15644692283686498</v>
+      </c>
+      <c r="Q8" cm="1">
+        <f t="array" ref="Q8">SUM(INDEX(contacts_original!$A$1:$P$16,
+           INT((ROW(Q8)-2)/5)+1,
+           INT((COLUMN(Q8)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
+        <v>4.1986461209260852</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(B9)-2)/5)+1,INT((COLUMN(B9)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="C9">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(C9)-2)/5)+1,INT((COLUMN(C9)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="D9">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(D9)-2)/5)+1,INT((COLUMN(D9)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="E9">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(E9)-2)/5)+1,INT((COLUMN(E9)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="F9">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(F9)-2)/5)+1,INT((COLUMN(F9)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="G9">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(G9)-2)/5)+1,INT((COLUMN(G9)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="H9">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(H9)-2)/5)+1,INT((COLUMN(H9)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="I9">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(I9)-2)/5)+1,INT((COLUMN(I9)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="J9">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(J9)-2)/5)+1,INT((COLUMN(J9)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="K9">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(K9)-2)/5)+1,INT((COLUMN(K9)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="L9">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(L9)-2)/5)+1,INT((COLUMN(L9)-2)/5)+1)/5</f>
+        <v>0.15644692283686498</v>
+      </c>
+      <c r="M9">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(M9)-2)/5)+1,INT((COLUMN(M9)-2)/5)+1)/5</f>
+        <v>0.15644692283686498</v>
+      </c>
+      <c r="N9">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(N9)-2)/5)+1,INT((COLUMN(N9)-2)/5)+1)/5</f>
+        <v>0.15644692283686498</v>
+      </c>
+      <c r="O9">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(O9)-2)/5)+1,INT((COLUMN(O9)-2)/5)+1)/5</f>
+        <v>0.15644692283686498</v>
+      </c>
+      <c r="P9">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(P9)-2)/5)+1,INT((COLUMN(P9)-2)/5)+1)/5</f>
+        <v>0.15644692283686498</v>
+      </c>
+      <c r="Q9" cm="1">
+        <f t="array" ref="Q9">SUM(INDEX(contacts_original!$A$1:$P$16,
+           INT((ROW(Q9)-2)/5)+1,
+           INT((COLUMN(Q9)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
+        <v>4.1986461209260852</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(B10)-2)/5)+1,INT((COLUMN(B10)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="C10">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(C10)-2)/5)+1,INT((COLUMN(C10)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="D10">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(D10)-2)/5)+1,INT((COLUMN(D10)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="E10">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(E10)-2)/5)+1,INT((COLUMN(E10)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="F10">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(F10)-2)/5)+1,INT((COLUMN(F10)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="G10">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(G10)-2)/5)+1,INT((COLUMN(G10)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="H10">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(H10)-2)/5)+1,INT((COLUMN(H10)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="I10">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(I10)-2)/5)+1,INT((COLUMN(I10)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="J10">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(J10)-2)/5)+1,INT((COLUMN(J10)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="K10">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(K10)-2)/5)+1,INT((COLUMN(K10)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="L10">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(L10)-2)/5)+1,INT((COLUMN(L10)-2)/5)+1)/5</f>
+        <v>0.15644692283686498</v>
+      </c>
+      <c r="M10">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(M10)-2)/5)+1,INT((COLUMN(M10)-2)/5)+1)/5</f>
+        <v>0.15644692283686498</v>
+      </c>
+      <c r="N10">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(N10)-2)/5)+1,INT((COLUMN(N10)-2)/5)+1)/5</f>
+        <v>0.15644692283686498</v>
+      </c>
+      <c r="O10">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(O10)-2)/5)+1,INT((COLUMN(O10)-2)/5)+1)/5</f>
+        <v>0.15644692283686498</v>
+      </c>
+      <c r="P10">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(P10)-2)/5)+1,INT((COLUMN(P10)-2)/5)+1)/5</f>
+        <v>0.15644692283686498</v>
+      </c>
+      <c r="Q10" cm="1">
+        <f t="array" ref="Q10">SUM(INDEX(contacts_original!$A$1:$P$16,
+           INT((ROW(Q10)-2)/5)+1,
+           INT((COLUMN(Q10)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
+        <v>4.1986461209260852</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(B11)-2)/5)+1,INT((COLUMN(B11)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="C11">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(C11)-2)/5)+1,INT((COLUMN(C11)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="D11">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(D11)-2)/5)+1,INT((COLUMN(D11)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="E11">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(E11)-2)/5)+1,INT((COLUMN(E11)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="F11">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(F11)-2)/5)+1,INT((COLUMN(F11)-2)/5)+1)/5</f>
+        <v>0.14959756223849122</v>
+      </c>
+      <c r="G11">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(G11)-2)/5)+1,INT((COLUMN(G11)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="H11">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(H11)-2)/5)+1,INT((COLUMN(H11)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="I11">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(I11)-2)/5)+1,INT((COLUMN(I11)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="J11">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(J11)-2)/5)+1,INT((COLUMN(J11)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="K11">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(K11)-2)/5)+1,INT((COLUMN(K11)-2)/5)+1)/5</f>
+        <v>0.8041641695669639</v>
+      </c>
+      <c r="L11">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(L11)-2)/5)+1,INT((COLUMN(L11)-2)/5)+1)/5</f>
+        <v>0.15644692283686498</v>
+      </c>
+      <c r="M11">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(M11)-2)/5)+1,INT((COLUMN(M11)-2)/5)+1)/5</f>
+        <v>0.15644692283686498</v>
+      </c>
+      <c r="N11">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(N11)-2)/5)+1,INT((COLUMN(N11)-2)/5)+1)/5</f>
+        <v>0.15644692283686498</v>
+      </c>
+      <c r="O11">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(O11)-2)/5)+1,INT((COLUMN(O11)-2)/5)+1)/5</f>
+        <v>0.15644692283686498</v>
+      </c>
+      <c r="P11">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(P11)-2)/5)+1,INT((COLUMN(P11)-2)/5)+1)/5</f>
+        <v>0.15644692283686498</v>
+      </c>
+      <c r="Q11" cm="1">
+        <f t="array" ref="Q11">SUM(INDEX(contacts_original!$A$1:$P$16,
+           INT((ROW(Q11)-2)/5)+1,
+           INT((COLUMN(Q11)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
+        <v>4.1986461209260852</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(B12)-2)/5)+1,INT((COLUMN(B12)-2)/5)+1)/5</f>
+        <v>3.6383572099779077E-2</v>
+      </c>
+      <c r="C12">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(C12)-2)/5)+1,INT((COLUMN(C12)-2)/5)+1)/5</f>
+        <v>3.6383572099779077E-2</v>
+      </c>
+      <c r="D12">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(D12)-2)/5)+1,INT((COLUMN(D12)-2)/5)+1)/5</f>
+        <v>3.6383572099779077E-2</v>
+      </c>
+      <c r="E12">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(E12)-2)/5)+1,INT((COLUMN(E12)-2)/5)+1)/5</f>
+        <v>3.6383572099779077E-2</v>
+      </c>
+      <c r="F12">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(F12)-2)/5)+1,INT((COLUMN(F12)-2)/5)+1)/5</f>
+        <v>3.6383572099779077E-2</v>
+      </c>
+      <c r="G12">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(G12)-2)/5)+1,INT((COLUMN(G12)-2)/5)+1)/5</f>
+        <v>0.25597002835030275</v>
+      </c>
+      <c r="H12">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(H12)-2)/5)+1,INT((COLUMN(H12)-2)/5)+1)/5</f>
+        <v>0.25597002835030275</v>
+      </c>
+      <c r="I12">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(I12)-2)/5)+1,INT((COLUMN(I12)-2)/5)+1)/5</f>
+        <v>0.25597002835030275</v>
+      </c>
+      <c r="J12">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(J12)-2)/5)+1,INT((COLUMN(J12)-2)/5)+1)/5</f>
+        <v>0.25597002835030275</v>
+      </c>
+      <c r="K12">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(K12)-2)/5)+1,INT((COLUMN(K12)-2)/5)+1)/5</f>
+        <v>0.25597002835030275</v>
+      </c>
+      <c r="L12">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(L12)-2)/5)+1,INT((COLUMN(L12)-2)/5)+1)/5</f>
+        <v>1.1920094334633184</v>
+      </c>
+      <c r="M12">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(M12)-2)/5)+1,INT((COLUMN(M12)-2)/5)+1)/5</f>
+        <v>1.1920094334633184</v>
+      </c>
+      <c r="N12">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(N12)-2)/5)+1,INT((COLUMN(N12)-2)/5)+1)/5</f>
+        <v>1.1920094334633184</v>
+      </c>
+      <c r="O12">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(O12)-2)/5)+1,INT((COLUMN(O12)-2)/5)+1)/5</f>
+        <v>1.1920094334633184</v>
+      </c>
+      <c r="P12">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(P12)-2)/5)+1,INT((COLUMN(P12)-2)/5)+1)/5</f>
+        <v>1.1920094334633184</v>
+      </c>
+      <c r="Q12" cm="1">
+        <f t="array" ref="Q12">SUM(INDEX(contacts_original!$A$1:$P$16,
+           INT((ROW(Q12)-2)/5)+1,
+           INT((COLUMN(Q12)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
+        <v>4.3374993891872862</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(B13)-2)/5)+1,INT((COLUMN(B13)-2)/5)+1)/5</f>
+        <v>3.6383572099779077E-2</v>
+      </c>
+      <c r="C13">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(C13)-2)/5)+1,INT((COLUMN(C13)-2)/5)+1)/5</f>
+        <v>3.6383572099779077E-2</v>
+      </c>
+      <c r="D13">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(D13)-2)/5)+1,INT((COLUMN(D13)-2)/5)+1)/5</f>
+        <v>3.6383572099779077E-2</v>
+      </c>
+      <c r="E13">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(E13)-2)/5)+1,INT((COLUMN(E13)-2)/5)+1)/5</f>
+        <v>3.6383572099779077E-2</v>
+      </c>
+      <c r="F13">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(F13)-2)/5)+1,INT((COLUMN(F13)-2)/5)+1)/5</f>
+        <v>3.6383572099779077E-2</v>
+      </c>
+      <c r="G13">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(G13)-2)/5)+1,INT((COLUMN(G13)-2)/5)+1)/5</f>
+        <v>0.25597002835030275</v>
+      </c>
+      <c r="H13">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(H13)-2)/5)+1,INT((COLUMN(H13)-2)/5)+1)/5</f>
+        <v>0.25597002835030275</v>
+      </c>
+      <c r="I13">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(I13)-2)/5)+1,INT((COLUMN(I13)-2)/5)+1)/5</f>
+        <v>0.25597002835030275</v>
+      </c>
+      <c r="J13">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(J13)-2)/5)+1,INT((COLUMN(J13)-2)/5)+1)/5</f>
+        <v>0.25597002835030275</v>
+      </c>
+      <c r="K13">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(K13)-2)/5)+1,INT((COLUMN(K13)-2)/5)+1)/5</f>
+        <v>0.25597002835030275</v>
+      </c>
+      <c r="L13">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(L13)-2)/5)+1,INT((COLUMN(L13)-2)/5)+1)/5</f>
+        <v>1.1920094334633184</v>
+      </c>
+      <c r="M13">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(M13)-2)/5)+1,INT((COLUMN(M13)-2)/5)+1)/5</f>
+        <v>1.1920094334633184</v>
+      </c>
+      <c r="N13">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(N13)-2)/5)+1,INT((COLUMN(N13)-2)/5)+1)/5</f>
+        <v>1.1920094334633184</v>
+      </c>
+      <c r="O13">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(O13)-2)/5)+1,INT((COLUMN(O13)-2)/5)+1)/5</f>
+        <v>1.1920094334633184</v>
+      </c>
+      <c r="P13">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(P13)-2)/5)+1,INT((COLUMN(P13)-2)/5)+1)/5</f>
+        <v>1.1920094334633184</v>
+      </c>
+      <c r="Q13" cm="1">
+        <f t="array" ref="Q13">SUM(INDEX(contacts_original!$A$1:$P$16,
+           INT((ROW(Q13)-2)/5)+1,
+           INT((COLUMN(Q13)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
+        <v>4.3374993891872862</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(B14)-2)/5)+1,INT((COLUMN(B14)-2)/5)+1)/5</f>
+        <v>3.6383572099779077E-2</v>
+      </c>
+      <c r="C14">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(C14)-2)/5)+1,INT((COLUMN(C14)-2)/5)+1)/5</f>
+        <v>3.6383572099779077E-2</v>
+      </c>
+      <c r="D14">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(D14)-2)/5)+1,INT((COLUMN(D14)-2)/5)+1)/5</f>
+        <v>3.6383572099779077E-2</v>
+      </c>
+      <c r="E14">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(E14)-2)/5)+1,INT((COLUMN(E14)-2)/5)+1)/5</f>
+        <v>3.6383572099779077E-2</v>
+      </c>
+      <c r="F14">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(F14)-2)/5)+1,INT((COLUMN(F14)-2)/5)+1)/5</f>
+        <v>3.6383572099779077E-2</v>
+      </c>
+      <c r="G14">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(G14)-2)/5)+1,INT((COLUMN(G14)-2)/5)+1)/5</f>
+        <v>0.25597002835030275</v>
+      </c>
+      <c r="H14">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(H14)-2)/5)+1,INT((COLUMN(H14)-2)/5)+1)/5</f>
+        <v>0.25597002835030275</v>
+      </c>
+      <c r="I14">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(I14)-2)/5)+1,INT((COLUMN(I14)-2)/5)+1)/5</f>
+        <v>0.25597002835030275</v>
+      </c>
+      <c r="J14">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(J14)-2)/5)+1,INT((COLUMN(J14)-2)/5)+1)/5</f>
+        <v>0.25597002835030275</v>
+      </c>
+      <c r="K14">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(K14)-2)/5)+1,INT((COLUMN(K14)-2)/5)+1)/5</f>
+        <v>0.25597002835030275</v>
+      </c>
+      <c r="L14">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(L14)-2)/5)+1,INT((COLUMN(L14)-2)/5)+1)/5</f>
+        <v>1.1920094334633184</v>
+      </c>
+      <c r="M14">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(M14)-2)/5)+1,INT((COLUMN(M14)-2)/5)+1)/5</f>
+        <v>1.1920094334633184</v>
+      </c>
+      <c r="N14">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(N14)-2)/5)+1,INT((COLUMN(N14)-2)/5)+1)/5</f>
+        <v>1.1920094334633184</v>
+      </c>
+      <c r="O14">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(O14)-2)/5)+1,INT((COLUMN(O14)-2)/5)+1)/5</f>
+        <v>1.1920094334633184</v>
+      </c>
+      <c r="P14">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(P14)-2)/5)+1,INT((COLUMN(P14)-2)/5)+1)/5</f>
+        <v>1.1920094334633184</v>
+      </c>
+      <c r="Q14" cm="1">
+        <f t="array" ref="Q14">SUM(INDEX(contacts_original!$A$1:$P$16,
+           INT((ROW(Q14)-2)/5)+1,
+           INT((COLUMN(Q14)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
+        <v>4.3374993891872862</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(B15)-2)/5)+1,INT((COLUMN(B15)-2)/5)+1)/5</f>
+        <v>3.6383572099779077E-2</v>
+      </c>
+      <c r="C15">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(C15)-2)/5)+1,INT((COLUMN(C15)-2)/5)+1)/5</f>
+        <v>3.6383572099779077E-2</v>
+      </c>
+      <c r="D15">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(D15)-2)/5)+1,INT((COLUMN(D15)-2)/5)+1)/5</f>
+        <v>3.6383572099779077E-2</v>
+      </c>
+      <c r="E15">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(E15)-2)/5)+1,INT((COLUMN(E15)-2)/5)+1)/5</f>
+        <v>3.6383572099779077E-2</v>
+      </c>
+      <c r="F15">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(F15)-2)/5)+1,INT((COLUMN(F15)-2)/5)+1)/5</f>
+        <v>3.6383572099779077E-2</v>
+      </c>
+      <c r="G15">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(G15)-2)/5)+1,INT((COLUMN(G15)-2)/5)+1)/5</f>
+        <v>0.25597002835030275</v>
+      </c>
+      <c r="H15">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(H15)-2)/5)+1,INT((COLUMN(H15)-2)/5)+1)/5</f>
+        <v>0.25597002835030275</v>
+      </c>
+      <c r="I15">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(I15)-2)/5)+1,INT((COLUMN(I15)-2)/5)+1)/5</f>
+        <v>0.25597002835030275</v>
+      </c>
+      <c r="J15">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(J15)-2)/5)+1,INT((COLUMN(J15)-2)/5)+1)/5</f>
+        <v>0.25597002835030275</v>
+      </c>
+      <c r="K15">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(K15)-2)/5)+1,INT((COLUMN(K15)-2)/5)+1)/5</f>
+        <v>0.25597002835030275</v>
+      </c>
+      <c r="L15">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(L15)-2)/5)+1,INT((COLUMN(L15)-2)/5)+1)/5</f>
+        <v>1.1920094334633184</v>
+      </c>
+      <c r="M15">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(M15)-2)/5)+1,INT((COLUMN(M15)-2)/5)+1)/5</f>
+        <v>1.1920094334633184</v>
+      </c>
+      <c r="N15">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(N15)-2)/5)+1,INT((COLUMN(N15)-2)/5)+1)/5</f>
+        <v>1.1920094334633184</v>
+      </c>
+      <c r="O15">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(O15)-2)/5)+1,INT((COLUMN(O15)-2)/5)+1)/5</f>
+        <v>1.1920094334633184</v>
+      </c>
+      <c r="P15">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(P15)-2)/5)+1,INT((COLUMN(P15)-2)/5)+1)/5</f>
+        <v>1.1920094334633184</v>
+      </c>
+      <c r="Q15" cm="1">
+        <f t="array" ref="Q15">SUM(INDEX(contacts_original!$A$1:$P$16,
+           INT((ROW(Q15)-2)/5)+1,
+           INT((COLUMN(Q15)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
+        <v>4.3374993891872862</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A16" s="1">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(B16)-2)/5)+1,INT((COLUMN(B16)-2)/5)+1)/5</f>
+        <v>3.6383572099779077E-2</v>
+      </c>
+      <c r="C16">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(C16)-2)/5)+1,INT((COLUMN(C16)-2)/5)+1)/5</f>
+        <v>3.6383572099779077E-2</v>
+      </c>
+      <c r="D16">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(D16)-2)/5)+1,INT((COLUMN(D16)-2)/5)+1)/5</f>
+        <v>3.6383572099779077E-2</v>
+      </c>
+      <c r="E16">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(E16)-2)/5)+1,INT((COLUMN(E16)-2)/5)+1)/5</f>
+        <v>3.6383572099779077E-2</v>
+      </c>
+      <c r="F16">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(F16)-2)/5)+1,INT((COLUMN(F16)-2)/5)+1)/5</f>
+        <v>3.6383572099779077E-2</v>
+      </c>
+      <c r="G16">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(G16)-2)/5)+1,INT((COLUMN(G16)-2)/5)+1)/5</f>
+        <v>0.25597002835030275</v>
+      </c>
+      <c r="H16">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(H16)-2)/5)+1,INT((COLUMN(H16)-2)/5)+1)/5</f>
+        <v>0.25597002835030275</v>
+      </c>
+      <c r="I16">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(I16)-2)/5)+1,INT((COLUMN(I16)-2)/5)+1)/5</f>
+        <v>0.25597002835030275</v>
+      </c>
+      <c r="J16">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(J16)-2)/5)+1,INT((COLUMN(J16)-2)/5)+1)/5</f>
+        <v>0.25597002835030275</v>
+      </c>
+      <c r="K16">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(K16)-2)/5)+1,INT((COLUMN(K16)-2)/5)+1)/5</f>
+        <v>0.25597002835030275</v>
+      </c>
+      <c r="L16">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(L16)-2)/5)+1,INT((COLUMN(L16)-2)/5)+1)/5</f>
+        <v>1.1920094334633184</v>
+      </c>
+      <c r="M16">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(M16)-2)/5)+1,INT((COLUMN(M16)-2)/5)+1)/5</f>
+        <v>1.1920094334633184</v>
+      </c>
+      <c r="N16">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(N16)-2)/5)+1,INT((COLUMN(N16)-2)/5)+1)/5</f>
+        <v>1.1920094334633184</v>
+      </c>
+      <c r="O16">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(O16)-2)/5)+1,INT((COLUMN(O16)-2)/5)+1)/5</f>
+        <v>1.1920094334633184</v>
+      </c>
+      <c r="P16">
+        <f>INDEX([1]contacts!$A$1:$P$16,INT((ROW(P16)-2)/5)+1,INT((COLUMN(P16)-2)/5)+1)/5</f>
+        <v>1.1920094334633184</v>
+      </c>
+      <c r="Q16" cm="1">
+        <f t="array" ref="Q16">SUM(INDEX(contacts_original!$A$1:$P$16,
+           INT((ROW(Q16)-2)/5)+1,
+           INT((COLUMN(Q16)-2)/5)+1 + _xlfn.SEQUENCE(13,1,0,1)))</f>
+        <v>4.3374993891872862</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" cm="1">
+        <f t="array" ref="B17">SUM(INDEX(contacts_original!$A$1:$P$16,
+INT((ROW(B17)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
+INT((COLUMN(B17)/5)+1)))</f>
+        <v>5.0410498887180362</v>
+      </c>
+      <c r="C17" cm="1">
+        <f t="array" ref="C17">SUM(INDEX(contacts_original!$A$1:$P$16,
+INT((ROW(C17)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
+INT((COLUMN(C17)/5)+1)))</f>
+        <v>5.0410498887180362</v>
+      </c>
+      <c r="D17" cm="1">
+        <f t="array" ref="D17">SUM(INDEX(contacts_original!$A$1:$P$16,
+INT((ROW(D17)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
+INT((COLUMN(D17)/5)+1)))</f>
+        <v>5.0410498887180362</v>
+      </c>
+      <c r="E17" cm="1">
+        <f t="array" ref="E17">SUM(INDEX(contacts_original!$A$1:$P$16,
+INT((ROW(E17)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
+INT((COLUMN(E17)/5)+1)))</f>
+        <v>7.1278811561401056</v>
+      </c>
+      <c r="F17" cm="1">
+        <f t="array" ref="F17">SUM(INDEX(contacts_original!$A$1:$P$16,
+INT((ROW(F17)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
+INT((COLUMN(F17)/5)+1)))</f>
+        <v>7.1278811561401056</v>
+      </c>
+      <c r="G17" cm="1">
+        <f t="array" ref="G17">SUM(INDEX(contacts_original!$A$1:$P$16,
+INT((ROW(G17)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
+INT((COLUMN(G17)/5)+1)))</f>
+        <v>7.1278811561401056</v>
+      </c>
+      <c r="H17" cm="1">
+        <f t="array" ref="H17">SUM(INDEX(contacts_original!$A$1:$P$16,
+INT((ROW(H17)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
+INT((COLUMN(H17)/5)+1)))</f>
+        <v>7.1278811561401056</v>
+      </c>
+      <c r="I17" cm="1">
+        <f t="array" ref="I17">SUM(INDEX(contacts_original!$A$1:$P$16,
+INT((ROW(I17)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
+INT((COLUMN(I17)/5)+1)))</f>
+        <v>7.1278811561401056</v>
+      </c>
+      <c r="J17" cm="1">
+        <f t="array" ref="J17">SUM(INDEX(contacts_original!$A$1:$P$16,
+INT((ROW(J17)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
+INT((COLUMN(J17)/5)+1)))</f>
+        <v>8.8624718507650364</v>
+      </c>
+      <c r="K17" cm="1">
+        <f t="array" ref="K17">SUM(INDEX(contacts_original!$A$1:$P$16,
+INT((ROW(K17)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
+INT((COLUMN(K17)/5)+1)))</f>
+        <v>8.8624718507650364</v>
+      </c>
+      <c r="L17" cm="1">
+        <f t="array" ref="L17">SUM(INDEX(contacts_original!$A$1:$P$16,
+INT((ROW(L17)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
+INT((COLUMN(L17)/5)+1)))</f>
+        <v>8.8624718507650364</v>
+      </c>
+      <c r="M17" cm="1">
+        <f t="array" ref="M17">SUM(INDEX(contacts_original!$A$1:$P$16,
+INT((ROW(M17)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
+INT((COLUMN(M17)/5)+1)))</f>
+        <v>8.8624718507650364</v>
+      </c>
+      <c r="N17" cm="1">
+        <f t="array" ref="N17">SUM(INDEX(contacts_original!$A$1:$P$16,
+INT((ROW(N17)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
+INT((COLUMN(N17)/5)+1)))</f>
+        <v>8.8624718507650364</v>
+      </c>
+      <c r="O17" cm="1">
+        <f t="array" ref="O17">SUM(INDEX(contacts_original!$A$1:$P$16,
+INT((ROW(O17)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
+INT((COLUMN(O17)/5)+1)))</f>
+        <v>18.641347197599554</v>
+      </c>
+      <c r="P17" cm="1">
+        <f t="array" ref="P17">SUM(INDEX(contacts_original!$A$1:$P$16,
+INT((ROW(P17)-2)/5)+1+_xlfn.SEQUENCE(13,1,0,1),
+INT((COLUMN(P17)/5)+1)))</f>
+        <v>18.641347197599554</v>
+      </c>
+      <c r="Q17">
+        <f>SUM(contacts_original!D4:P16)/(ROW(P16)-ROW(D4))</f>
+        <v>11.77072155631879</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
